--- a/output/final_deliverables/screener_output.xlsx
+++ b/output/final_deliverables/screener_output.xlsx
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Report Generated: 2026-08-19 10:25:19</t>
+          <t>Report Generated: 2026-08-20 10:04:51</t>
         </is>
       </c>
     </row>
